--- a/templates/gabarit_officiel.xlsx
+++ b/templates/gabarit_officiel.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuille" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUP" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -92,26 +93,22 @@
     <font>
       <name val="Aptos Narrow"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <color rgb="FFFF0000"/>
+      <name val="Courier"/>
+      <charset val="1"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF333332"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="70">
@@ -530,7 +527,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -580,9 +577,29 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -596,6 +613,19 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -618,14 +648,76 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,18 +732,22 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -663,30 +759,15 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,6 +812,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -996,38 +1080,74 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="60" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="60" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="60" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="60" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1361,8 +1481,6 @@
   <dimension ref="A1:GG4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14.5703125" customWidth="1" min="3" max="3"/>
     <col width="11.42578125" customWidth="1" min="6" max="187"/>
   </cols>
   <sheetData>
@@ -1498,7 +1616,7 @@
       <c r="DT1" s="5" t="n"/>
       <c r="DU1" s="5" t="n"/>
       <c r="DV1" s="5" t="n"/>
-      <c r="DW1" s="81" t="n"/>
+      <c r="DW1" s="82" t="n"/>
       <c r="DX1" s="5" t="n"/>
       <c r="DY1" s="5" t="n"/>
       <c r="DZ1" s="5" t="n"/>
@@ -1726,26 +1844,26 @@
           <t>natur et milieu ( milieu)</t>
         </is>
       </c>
-      <c r="DF2" s="115" t="inlineStr">
+      <c r="DF2" s="134" t="inlineStr">
         <is>
           <t>natur et milieu ( milieu)</t>
         </is>
       </c>
-      <c r="DG2" s="128" t="n"/>
-      <c r="DH2" s="128" t="n"/>
-      <c r="DI2" s="128" t="n"/>
-      <c r="DJ2" s="128" t="n"/>
-      <c r="DK2" s="128" t="n"/>
-      <c r="DL2" s="128" t="n"/>
-      <c r="DM2" s="128" t="n"/>
-      <c r="DN2" s="128" t="n"/>
-      <c r="DO2" s="128" t="n"/>
-      <c r="DP2" s="128" t="n"/>
-      <c r="DQ2" s="128" t="n"/>
-      <c r="DR2" s="113" t="n"/>
-      <c r="DS2" s="113" t="n"/>
-      <c r="DT2" s="113" t="n"/>
-      <c r="DU2" s="113" t="n"/>
+      <c r="DG2" s="135" t="n"/>
+      <c r="DH2" s="135" t="n"/>
+      <c r="DI2" s="135" t="n"/>
+      <c r="DJ2" s="135" t="n"/>
+      <c r="DK2" s="135" t="n"/>
+      <c r="DL2" s="135" t="n"/>
+      <c r="DM2" s="135" t="n"/>
+      <c r="DN2" s="135" t="n"/>
+      <c r="DO2" s="135" t="n"/>
+      <c r="DP2" s="135" t="n"/>
+      <c r="DQ2" s="136" t="n"/>
+      <c r="DR2" s="120" t="n"/>
+      <c r="DS2" s="120" t="n"/>
+      <c r="DT2" s="120" t="n"/>
+      <c r="DU2" s="120" t="n"/>
       <c r="DV2" s="17" t="inlineStr">
         <is>
           <t>natur et milieu (WATER)</t>
@@ -1884,7 +2002,7 @@
           <t>Landinrichting</t>
         </is>
       </c>
-      <c r="FA2" s="127" t="inlineStr">
+      <c r="FA2" s="20" t="inlineStr">
         <is>
           <t>Landinrichting
 Ruilverkaveling van landeigendommen uit kracht van wet</t>
@@ -1935,38 +2053,38 @@
           <t>Bouwen en wonen ( Geluidsbelasting)</t>
         </is>
       </c>
-      <c r="FL2" s="20" t="n"/>
-      <c r="FM2" s="20" t="n"/>
-      <c r="FN2" s="20" t="n"/>
-      <c r="FO2" s="20" t="n"/>
+      <c r="FL2" s="21" t="n"/>
+      <c r="FM2" s="21" t="n"/>
+      <c r="FN2" s="21" t="n"/>
+      <c r="FO2" s="21" t="n"/>
       <c r="FP2" s="17" t="inlineStr">
         <is>
           <t>Bouwen en wonen ( Geluidsbelasting)</t>
         </is>
       </c>
-      <c r="FQ2" s="20" t="n"/>
-      <c r="FR2" s="20" t="n"/>
-      <c r="FS2" s="20" t="n"/>
-      <c r="FT2" s="20" t="n"/>
+      <c r="FQ2" s="21" t="n"/>
+      <c r="FR2" s="21" t="n"/>
+      <c r="FS2" s="21" t="n"/>
+      <c r="FT2" s="21" t="n"/>
       <c r="FU2" s="17" t="inlineStr">
         <is>
           <t>Bouwen en wonen ( Geluidsbelasting)</t>
         </is>
       </c>
-      <c r="FV2" s="21" t="n"/>
-      <c r="FW2" s="21" t="n"/>
-      <c r="FX2" s="21" t="n"/>
-      <c r="FY2" s="21" t="n"/>
+      <c r="FV2" s="22" t="n"/>
+      <c r="FW2" s="22" t="n"/>
+      <c r="FX2" s="22" t="n"/>
+      <c r="FY2" s="22" t="n"/>
       <c r="FZ2" s="9" t="inlineStr">
         <is>
           <t>Etat des sols -mj https://www.degrotegrondvraag.be/</t>
         </is>
       </c>
-      <c r="GA2" s="21" t="n"/>
-      <c r="GB2" s="21" t="n"/>
-      <c r="GC2" s="21" t="n"/>
-      <c r="GD2" s="21" t="n"/>
-      <c r="GE2" s="21" t="n"/>
+      <c r="GA2" s="22" t="n"/>
+      <c r="GB2" s="22" t="n"/>
+      <c r="GC2" s="22" t="n"/>
+      <c r="GD2" s="22" t="n"/>
+      <c r="GE2" s="22" t="n"/>
       <c r="GF2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> Code du logement (Bouwen en wonen ,Vlaamse wooncode)</t>
@@ -1974,68 +2092,68 @@
       </c>
       <c r="GG2" s="9" t="n"/>
     </row>
-    <row r="3" ht="50.25" customHeight="1">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="22" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="24" t="n"/>
-      <c r="E3" s="24" t="n"/>
-      <c r="F3" s="25" t="inlineStr">
+    <row r="3" ht="63.75" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>Woongebieden</t>
         </is>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>Woonuitbreidingsgebieden</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>Woonparken</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t>Woongebieden met een landelijk karakter</t>
         </is>
       </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="J3" s="26" t="inlineStr">
         <is>
           <t>Woongebieden met culturelke, historische en/of esthetische waarde</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>Gebied voor kernontwikkeling</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="L3" s="31" t="inlineStr">
         <is>
           <t>Industriegebieden</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t>Gebieden voor vervuilende industrieën</t>
         </is>
       </c>
-      <c r="N3" s="30" t="inlineStr">
+      <c r="N3" s="31" t="inlineStr">
         <is>
           <t>Gebieden voor milieubelastende industrieën</t>
         </is>
       </c>
-      <c r="O3" s="31" t="inlineStr">
+      <c r="O3" s="32" t="inlineStr">
         <is>
           <t>Gebieden voor ambachtelijke bedrijven en de gebieden voor kleine en middelgrote ondernemingen</t>
         </is>
       </c>
-      <c r="P3" s="32" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t>Dienstverleningsgebieden (D)</t>
         </is>
       </c>
-      <c r="Q3" s="32" t="inlineStr">
+      <c r="Q3" s="33" t="inlineStr">
         <is>
           <t>Gebieden hoofdzakelijk besteld voor de vestiging van grootwinkelbedrijven</t>
         </is>
@@ -2045,592 +2163,592 @@
           <t>Landelijke gebieden</t>
         </is>
       </c>
-      <c r="S3" s="33" t="inlineStr">
+      <c r="S3" s="34" t="inlineStr">
         <is>
           <t>Agrarische gebieden</t>
         </is>
       </c>
-      <c r="T3" s="34" t="inlineStr">
+      <c r="T3" s="35" t="inlineStr">
         <is>
           <t>Bosgebieden</t>
         </is>
       </c>
-      <c r="U3" s="35" t="inlineStr">
+      <c r="U3" s="36" t="inlineStr">
         <is>
           <t>Groengebieden</t>
         </is>
       </c>
-      <c r="V3" s="35" t="inlineStr">
+      <c r="V3" s="36" t="inlineStr">
         <is>
           <t>Natuurgebieden (N)</t>
         </is>
       </c>
-      <c r="W3" s="35" t="inlineStr">
+      <c r="W3" s="36" t="inlineStr">
         <is>
           <t>Natuurgebieden met wetenschappelijke waarde of natuurreservaten ®</t>
         </is>
       </c>
-      <c r="X3" s="35" t="inlineStr">
+      <c r="X3" s="36" t="inlineStr">
         <is>
           <t>Parkgebieden (P)</t>
         </is>
       </c>
-      <c r="Y3" s="35" t="inlineStr">
+      <c r="Y3" s="36" t="inlineStr">
         <is>
           <t>Buffe"rzones (T)</t>
         </is>
       </c>
-      <c r="Z3" s="36" t="inlineStr">
+      <c r="Z3" s="37" t="inlineStr">
         <is>
           <t>Landschappelijke waarevolle gebieden</t>
         </is>
       </c>
-      <c r="AA3" s="37" t="inlineStr">
+      <c r="AA3" s="38" t="inlineStr">
         <is>
           <t>Recreatiegebieden</t>
         </is>
       </c>
-      <c r="AB3" s="37" t="inlineStr">
+      <c r="AB3" s="38" t="inlineStr">
         <is>
           <t>Landelijke gebieen met toeristische waarde</t>
         </is>
       </c>
-      <c r="AC3" s="38" t="inlineStr">
+      <c r="AC3" s="39" t="inlineStr">
         <is>
           <t>Gebieden voor gemeenschapsvoorzieningen en openbare nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="AD3" s="39" t="inlineStr">
+      <c r="AD3" s="40" t="inlineStr">
         <is>
           <t>Ontginningsgebieden</t>
         </is>
       </c>
-      <c r="AE3" s="101" t="inlineStr">
+      <c r="AE3" s="102" t="inlineStr">
         <is>
           <t>Gebieden voor dagrecreatie</t>
         </is>
       </c>
-      <c r="AF3" s="40" t="inlineStr">
+      <c r="AF3" s="41" t="inlineStr">
         <is>
           <t>Lien plan d'execution REGION</t>
         </is>
       </c>
-      <c r="AG3" s="40" t="inlineStr">
+      <c r="AG3" s="41" t="inlineStr">
         <is>
           <t>RUP</t>
         </is>
       </c>
-      <c r="AH3" s="25" t="inlineStr">
+      <c r="AH3" s="26" t="inlineStr">
         <is>
           <t>Wonen (zone d'habitat)</t>
         </is>
       </c>
-      <c r="AI3" s="25" t="inlineStr">
+      <c r="AI3" s="26" t="inlineStr">
         <is>
           <t>Zone voor kleinschalig wonen</t>
         </is>
       </c>
-      <c r="AJ3" s="41" t="inlineStr">
+      <c r="AJ3" s="42" t="inlineStr">
         <is>
           <t>Bedrijvigheid</t>
         </is>
       </c>
-      <c r="AK3" s="42" t="inlineStr">
+      <c r="AK3" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Bedrijvigheid - Buffer
 </t>
         </is>
       </c>
-      <c r="AL3" s="37" t="inlineStr">
+      <c r="AL3" s="38" t="inlineStr">
         <is>
           <t>Recreatie</t>
         </is>
       </c>
-      <c r="AM3" s="37" t="inlineStr">
+      <c r="AM3" s="38" t="inlineStr">
         <is>
           <t>Recreatie (Natuurverwerving)</t>
         </is>
       </c>
-      <c r="AN3" s="33" t="inlineStr">
+      <c r="AN3" s="34" t="inlineStr">
         <is>
           <t>Landbouw- agrarisch gebied</t>
         </is>
       </c>
-      <c r="AO3" s="43" t="inlineStr">
+      <c r="AO3" s="44" t="inlineStr">
         <is>
           <t>Landbouw- agrarische bedrijvenzone</t>
         </is>
       </c>
-      <c r="AP3" s="44" t="inlineStr">
+      <c r="AP3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- bouwvrij agrarisch gebied</t>
         </is>
       </c>
-      <c r="AQ3" s="44" t="inlineStr">
+      <c r="AQ3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- Agrarisch gebied met ecologisch belang</t>
         </is>
       </c>
-      <c r="AR3" s="45" t="inlineStr">
+      <c r="AR3" s="46" t="inlineStr">
         <is>
           <t>Bois (Bos)</t>
         </is>
       </c>
-      <c r="AS3" s="46" t="inlineStr">
+      <c r="AS3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen - gemengd openruimtegebied)</t>
         </is>
       </c>
-      <c r="AT3" s="46" t="inlineStr">
+      <c r="AT3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen- parkgebied)</t>
         </is>
       </c>
-      <c r="AU3" s="46" t="inlineStr">
+      <c r="AU3" s="47" t="inlineStr">
         <is>
           <t>Zone verte - Overig groen-Gemengd openruimtegebied met cultuurhistorische waarde</t>
         </is>
       </c>
-      <c r="AV3" s="46" t="inlineStr">
+      <c r="AV3" s="47" t="inlineStr">
         <is>
           <t>Zone verte- Overig groen -bestaande, vergunde of vergund geachte weekendverblijven</t>
         </is>
       </c>
-      <c r="AW3" s="47" t="inlineStr">
+      <c r="AW3" s="48" t="inlineStr">
         <is>
           <t>Natuurgebied</t>
         </is>
       </c>
-      <c r="AX3" s="47" t="inlineStr">
+      <c r="AX3" s="48" t="inlineStr">
         <is>
           <t>Natuurreservaat</t>
         </is>
       </c>
-      <c r="AY3" s="48" t="inlineStr">
+      <c r="AY3" s="49" t="inlineStr">
         <is>
           <t>Gemeenschaps- en nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="AZ3" s="48" t="inlineStr">
+      <c r="AZ3" s="49" t="inlineStr">
         <is>
           <t>Gebied voor zuiveringsinfrastructuur voor afvalwater</t>
         </is>
       </c>
-      <c r="BA3" s="48" t="inlineStr">
+      <c r="BA3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor infrastructuur voor duurzame watervoorziening </t>
         </is>
       </c>
-      <c r="BB3" s="48" t="inlineStr">
+      <c r="BB3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">
 gebied voor de winning van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="BC3" s="48" t="inlineStr">
+      <c r="BC3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor verwerking van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="BD3" s="49" t="inlineStr">
+      <c r="BD3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebied voor projectgrindwinning
 </t>
         </is>
       </c>
-      <c r="BE3" s="40" t="inlineStr">
+      <c r="BE3" s="41" t="inlineStr">
         <is>
           <t>Lien plman d'execution PROVINCE</t>
         </is>
       </c>
-      <c r="BF3" s="40" t="inlineStr">
+      <c r="BF3" s="41" t="inlineStr">
         <is>
           <t>RUP</t>
         </is>
       </c>
-      <c r="BG3" s="25" t="inlineStr">
+      <c r="BG3" s="26" t="inlineStr">
         <is>
           <t>Wonen (zone d'habitat)</t>
         </is>
       </c>
-      <c r="BH3" s="25" t="inlineStr">
+      <c r="BH3" s="26" t="inlineStr">
         <is>
           <t>Zone voor kleinschalig wonen</t>
         </is>
       </c>
-      <c r="BI3" s="41" t="inlineStr">
+      <c r="BI3" s="42" t="inlineStr">
         <is>
           <t>Bedrijvigheid</t>
         </is>
       </c>
-      <c r="BJ3" s="41" t="inlineStr">
+      <c r="BJ3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Bedrijvigheid - Buffer
 </t>
         </is>
       </c>
-      <c r="BK3" s="37" t="inlineStr">
+      <c r="BK3" s="38" t="inlineStr">
         <is>
           <t>Recreatie</t>
         </is>
       </c>
-      <c r="BL3" s="37" t="inlineStr">
+      <c r="BL3" s="38" t="inlineStr">
         <is>
           <t>Recreatie (Natuurverwerving)</t>
         </is>
       </c>
-      <c r="BM3" s="33" t="inlineStr">
+      <c r="BM3" s="34" t="inlineStr">
         <is>
           <t>Landbouw- agrarisch gebied</t>
         </is>
       </c>
-      <c r="BN3" s="44" t="inlineStr">
+      <c r="BN3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- agrarische bedrijvenzone</t>
         </is>
       </c>
-      <c r="BO3" s="44" t="inlineStr">
+      <c r="BO3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- bouwvrij agrarisch gebied</t>
         </is>
       </c>
-      <c r="BP3" s="44" t="inlineStr">
+      <c r="BP3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- Agrarisch gebied met ecologisch belang</t>
         </is>
       </c>
-      <c r="BQ3" s="45" t="inlineStr">
+      <c r="BQ3" s="46" t="inlineStr">
         <is>
           <t>Bois (Bos)</t>
         </is>
       </c>
-      <c r="BR3" s="46" t="inlineStr">
+      <c r="BR3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen - gemengd openruimtegebied)</t>
         </is>
       </c>
-      <c r="BS3" s="46" t="inlineStr">
+      <c r="BS3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen- parkgebied)</t>
         </is>
       </c>
-      <c r="BT3" s="46" t="inlineStr">
+      <c r="BT3" s="47" t="inlineStr">
         <is>
           <t>Zone verte - Overig groen-Gemengd openruimtegebied met cultuurhistorische waarde</t>
         </is>
       </c>
-      <c r="BU3" s="46" t="inlineStr">
+      <c r="BU3" s="47" t="inlineStr">
         <is>
           <t>Zone verte- Overig groen -bestaande, vergunde of vergund geachte weekendverblijven</t>
         </is>
       </c>
-      <c r="BV3" s="47" t="inlineStr">
+      <c r="BV3" s="48" t="inlineStr">
         <is>
           <t>Natuurgebied</t>
         </is>
       </c>
-      <c r="BW3" s="47" t="inlineStr">
+      <c r="BW3" s="48" t="inlineStr">
         <is>
           <t>Natuurreservaat</t>
         </is>
       </c>
-      <c r="BX3" s="48" t="inlineStr">
+      <c r="BX3" s="49" t="inlineStr">
         <is>
           <t>Gemeenschaps- en nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="BY3" s="48" t="inlineStr">
+      <c r="BY3" s="49" t="inlineStr">
         <is>
           <t>Gebied voor zuiveringsinfrastructuur voor afvalwater</t>
         </is>
       </c>
-      <c r="BZ3" s="48" t="inlineStr">
+      <c r="BZ3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor infrastructuur voor duurzame watervoorziening </t>
         </is>
       </c>
-      <c r="CA3" s="48" t="inlineStr">
+      <c r="CA3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">
 gebied voor de winning van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="CB3" s="48" t="inlineStr">
+      <c r="CB3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor verwerking van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="CC3" s="49" t="inlineStr">
+      <c r="CC3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebied voor projectgrindwinning
 </t>
         </is>
       </c>
-      <c r="CD3" s="40" t="inlineStr">
+      <c r="CD3" s="41" t="inlineStr">
         <is>
           <t>Lien  d'execution commune</t>
         </is>
       </c>
-      <c r="CE3" s="40" t="inlineStr">
+      <c r="CE3" s="41" t="inlineStr">
         <is>
           <t>RUP</t>
         </is>
       </c>
-      <c r="CF3" s="25" t="inlineStr">
+      <c r="CF3" s="26" t="inlineStr">
         <is>
           <t>Wonen (zone d'habitat)</t>
         </is>
       </c>
-      <c r="CG3" s="25" t="inlineStr">
+      <c r="CG3" s="26" t="inlineStr">
         <is>
           <t>Zone voor kleinschalig wonen</t>
         </is>
       </c>
-      <c r="CH3" s="41" t="inlineStr">
+      <c r="CH3" s="42" t="inlineStr">
         <is>
           <t>Bedrijvigheid</t>
         </is>
       </c>
-      <c r="CI3" s="50" t="inlineStr">
+      <c r="CI3" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">Bedrijvigheid - Buffer
 </t>
         </is>
       </c>
-      <c r="CJ3" s="37" t="inlineStr">
+      <c r="CJ3" s="38" t="inlineStr">
         <is>
           <t>Recreatie</t>
         </is>
       </c>
-      <c r="CK3" s="37" t="inlineStr">
+      <c r="CK3" s="38" t="inlineStr">
         <is>
           <t>Recreatie (Natuurverwerving)</t>
         </is>
       </c>
-      <c r="CL3" s="44" t="inlineStr">
+      <c r="CL3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- agrarisch gebied</t>
         </is>
       </c>
-      <c r="CM3" s="44" t="inlineStr">
+      <c r="CM3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- agrarische bedrijvenzone</t>
         </is>
       </c>
-      <c r="CN3" s="44" t="inlineStr">
+      <c r="CN3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- bouwvrij agrarisch gebied</t>
         </is>
       </c>
-      <c r="CO3" s="44" t="inlineStr">
+      <c r="CO3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- Agrarisch gebied met ecologisch belang</t>
         </is>
       </c>
-      <c r="CP3" s="45" t="inlineStr">
+      <c r="CP3" s="46" t="inlineStr">
         <is>
           <t>Bois (Bos)</t>
         </is>
       </c>
-      <c r="CQ3" s="46" t="inlineStr">
+      <c r="CQ3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen - gemengd openruimtegebied)</t>
         </is>
       </c>
-      <c r="CR3" s="46" t="inlineStr">
+      <c r="CR3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen- parkgebied)</t>
         </is>
       </c>
-      <c r="CS3" s="46" t="inlineStr">
+      <c r="CS3" s="47" t="inlineStr">
         <is>
           <t>Zone verte - Overig groen-Gemengd openruimtegebied met cultuurhistorische waarde</t>
         </is>
       </c>
-      <c r="CT3" s="46" t="inlineStr">
+      <c r="CT3" s="47" t="inlineStr">
         <is>
           <t>Zone verte- Overig groen -bestaande, vergunde of vergund geachte weekendverblijven</t>
         </is>
       </c>
-      <c r="CU3" s="47" t="inlineStr">
+      <c r="CU3" s="48" t="inlineStr">
         <is>
           <t>Natuurgebied</t>
         </is>
       </c>
-      <c r="CV3" s="47" t="inlineStr">
+      <c r="CV3" s="48" t="inlineStr">
         <is>
           <t>Natuurreservaat</t>
         </is>
       </c>
-      <c r="CW3" s="48" t="inlineStr">
+      <c r="CW3" s="49" t="inlineStr">
         <is>
           <t>Gemeenschaps- en nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="CX3" s="48" t="inlineStr">
+      <c r="CX3" s="49" t="inlineStr">
         <is>
           <t>Gebied voor zuiveringsinfrastructuur voor afvalwater</t>
         </is>
       </c>
-      <c r="CY3" s="48" t="inlineStr">
+      <c r="CY3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor infrastructuur voor duurzame watervoorziening </t>
         </is>
       </c>
-      <c r="CZ3" s="51" t="inlineStr">
+      <c r="CZ3" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">
 gebied voor de winning van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="DA3" s="48" t="inlineStr">
+      <c r="DA3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor verwerking van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="DB3" s="49" t="inlineStr">
+      <c r="DB3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebied voor projectgrindwinning
 </t>
         </is>
       </c>
-      <c r="DC3" s="102" t="inlineStr">
+      <c r="DC3" s="103" t="inlineStr">
         <is>
           <t>Mogelijk overstromingsgevoelig</t>
         </is>
       </c>
-      <c r="DD3" s="52" t="inlineStr">
+      <c r="DD3" s="53" t="inlineStr">
         <is>
           <t>Effectief overstromingsgevoelig</t>
         </is>
       </c>
-      <c r="DE3" s="53" t="inlineStr">
+      <c r="DE3" s="54" t="inlineStr">
         <is>
           <t>Beheergebieden beheerovereenkomst waterwaliteit</t>
         </is>
       </c>
-      <c r="DF3" s="116" t="inlineStr">
+      <c r="DF3" s="121" t="inlineStr">
         <is>
           <t>Overstromingsgevoelige gebieden  Pluvial</t>
         </is>
       </c>
-      <c r="DG3" s="129" t="n"/>
-      <c r="DH3" s="129" t="n"/>
-      <c r="DI3" s="129" t="n"/>
-      <c r="DJ3" s="116" t="inlineStr">
+      <c r="DG3" s="137" t="n"/>
+      <c r="DH3" s="137" t="n"/>
+      <c r="DI3" s="137" t="n"/>
+      <c r="DJ3" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">Overstromingsgevoelige gebieden Fluvial </t>
         </is>
       </c>
-      <c r="DK3" s="129" t="n"/>
-      <c r="DL3" s="129" t="n"/>
-      <c r="DM3" s="129" t="n"/>
-      <c r="DN3" s="117" t="inlineStr">
+      <c r="DK3" s="137" t="n"/>
+      <c r="DL3" s="137" t="n"/>
+      <c r="DM3" s="137" t="n"/>
+      <c r="DN3" s="123" t="inlineStr">
         <is>
           <t>Overstromingsgevoelige gebieden vanuit zee</t>
         </is>
       </c>
-      <c r="DO3" s="129" t="n"/>
-      <c r="DP3" s="129" t="n"/>
-      <c r="DQ3" s="130" t="n"/>
-      <c r="DR3" s="114" t="inlineStr">
+      <c r="DO3" s="137" t="n"/>
+      <c r="DP3" s="137" t="n"/>
+      <c r="DQ3" s="138" t="n"/>
+      <c r="DR3" s="139" t="inlineStr">
         <is>
           <t>Afgebakende overstromingsgebieden en oeverzones</t>
         </is>
       </c>
-      <c r="DS3" s="129" t="n"/>
-      <c r="DT3" s="114" t="inlineStr">
+      <c r="DS3" s="138" t="n"/>
+      <c r="DT3" s="139" t="inlineStr">
         <is>
           <t>Signaalgebieden</t>
         </is>
       </c>
-      <c r="DU3" s="129" t="n"/>
-      <c r="DV3" s="54" t="inlineStr">
+      <c r="DU3" s="138" t="n"/>
+      <c r="DV3" s="55" t="inlineStr">
         <is>
           <t>Grond waterstromingsgevoelige gebieden</t>
         </is>
       </c>
-      <c r="DW3" s="55" t="inlineStr">
+      <c r="DW3" s="56" t="inlineStr">
         <is>
           <t>Van Natuur overstroombare gebieden</t>
         </is>
       </c>
-      <c r="DX3" s="56" t="inlineStr">
+      <c r="DX3" s="57" t="inlineStr">
         <is>
           <t>Risicozones voor overstromingen: nieuwe en bevestigde risocozones</t>
         </is>
       </c>
-      <c r="DY3" s="57" t="inlineStr">
+      <c r="DY3" s="58" t="inlineStr">
         <is>
           <t>Recent overstromde gebieden</t>
         </is>
       </c>
-      <c r="DZ3" s="58" t="inlineStr">
+      <c r="DZ3" s="59" t="inlineStr">
         <is>
           <t>Overstromingsgebieden en oeverzones - integraal waterbeleid</t>
         </is>
       </c>
-      <c r="EA3" s="59" t="inlineStr">
+      <c r="EA3" s="60" t="inlineStr">
         <is>
           <t>Grondwaterwingebieden en beschermingszones</t>
         </is>
       </c>
-      <c r="EB3" s="60" t="inlineStr">
+      <c r="EB3" s="61" t="inlineStr">
         <is>
           <t>Infiltratiegevoelige bodems</t>
         </is>
       </c>
-      <c r="EC3" s="58" t="inlineStr">
+      <c r="EC3" s="59" t="inlineStr">
         <is>
           <t>Afstromingskaart (enkelvoudige stroomlijnen)</t>
         </is>
       </c>
-      <c r="ED3" s="58" t="n"/>
-      <c r="EE3" s="58" t="n"/>
-      <c r="EF3" s="58" t="n"/>
-      <c r="EG3" s="58" t="n"/>
-      <c r="EH3" s="58" t="n"/>
-      <c r="EI3" s="103" t="inlineStr">
+      <c r="ED3" s="59" t="n"/>
+      <c r="EE3" s="59" t="n"/>
+      <c r="EF3" s="59" t="n"/>
+      <c r="EG3" s="59" t="n"/>
+      <c r="EH3" s="59" t="n"/>
+      <c r="EI3" s="104" t="inlineStr">
         <is>
           <t>Andere erosiegerelateerde gronden</t>
         </is>
       </c>
-      <c r="EJ3" s="56" t="inlineStr">
+      <c r="EJ3" s="57" t="inlineStr">
         <is>
           <t>Gekarteerde grondverschuivingen</t>
         </is>
       </c>
-      <c r="EK3" s="61" t="inlineStr">
+      <c r="EK3" s="62" t="inlineStr">
         <is>
           <t>Gevoeligheid voor grondverschuivingen</t>
         </is>
       </c>
-      <c r="EL3" s="62" t="inlineStr">
+      <c r="EL3" s="63" t="inlineStr">
         <is>
           <t>Potentiële bodemerosiekaart per perceel 2021</t>
         </is>
       </c>
-      <c r="EM3" s="63" t="inlineStr">
+      <c r="EM3" s="64" t="inlineStr">
         <is>
           <t>Watertoets</t>
         </is>
       </c>
-      <c r="EN3" s="64" t="inlineStr">
+      <c r="EN3" s="65" t="inlineStr">
         <is>
           <t>Aangeboden bedrijventerreinperceel</t>
         </is>
       </c>
-      <c r="EO3" s="59" t="inlineStr">
+      <c r="EO3" s="60" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
         </is>
       </c>
-      <c r="EP3" s="59" t="inlineStr">
+      <c r="EP3" s="60" t="inlineStr">
         <is>
           <t>Beheerde bedrijvenzone</t>
         </is>
       </c>
-      <c r="EQ3" s="65" t="inlineStr">
+      <c r="EQ3" s="66" t="inlineStr">
         <is>
           <t>Ontwikkelbare bedrijvenzone</t>
         </is>
@@ -2640,99 +2758,99 @@
           <t>Planningszone met economische bestemming</t>
         </is>
       </c>
-      <c r="ES3" s="66" t="inlineStr">
+      <c r="ES3" s="67" t="inlineStr">
         <is>
           <t>Brownfieldconvenanten</t>
         </is>
       </c>
-      <c r="ET3" s="59" t="inlineStr">
+      <c r="ET3" s="60" t="inlineStr">
         <is>
           <t>Steunzone</t>
         </is>
       </c>
-      <c r="EU3" s="67" t="inlineStr">
+      <c r="EU3" s="68" t="inlineStr">
         <is>
           <t>Seveso inrichingen</t>
         </is>
       </c>
-      <c r="EV3" s="68" t="inlineStr">
+      <c r="EV3" s="69" t="inlineStr">
         <is>
           <t>Consultatie zone van Seveso-inrichtingen</t>
         </is>
       </c>
-      <c r="EW3" s="43" t="inlineStr">
+      <c r="EW3" s="44" t="inlineStr">
         <is>
           <t>Landinrichting in onderzoek</t>
         </is>
       </c>
-      <c r="EX3" s="69" t="inlineStr">
+      <c r="EX3" s="70" t="inlineStr">
         <is>
           <t>Vastgesteld landinrichtingsproject</t>
         </is>
       </c>
-      <c r="EY3" s="70" t="inlineStr">
+      <c r="EY3" s="71" t="inlineStr">
         <is>
           <t>Landinrichtingsplan</t>
         </is>
       </c>
-      <c r="EZ3" s="35" t="inlineStr">
+      <c r="EZ3" s="36" t="inlineStr">
         <is>
           <t>Natuurinrichting</t>
         </is>
       </c>
-      <c r="FA3" s="25" t="inlineStr">
+      <c r="FA3" s="26" t="inlineStr">
         <is>
           <t>Ruilverkaveling
 (Ruilverkaveling van landeigendommen uit kracht van wet)</t>
         </is>
       </c>
-      <c r="FB3" s="71" t="inlineStr">
+      <c r="FB3" s="72" t="inlineStr">
         <is>
           <t>Fysische systeemeenheden</t>
         </is>
       </c>
-      <c r="FC3" s="72" t="inlineStr">
+      <c r="FC3" s="73" t="inlineStr">
         <is>
           <t>Traditionele landschappen</t>
         </is>
       </c>
-      <c r="FD3" s="61" t="inlineStr">
+      <c r="FD3" s="62" t="inlineStr">
         <is>
           <t>Beheergebieden Natura 2000-soorten</t>
         </is>
       </c>
-      <c r="FE3" s="73" t="inlineStr">
+      <c r="FE3" s="74" t="inlineStr">
         <is>
           <t>Bosreservaten</t>
         </is>
       </c>
-      <c r="FF3" s="65" t="inlineStr">
+      <c r="FF3" s="66" t="inlineStr">
         <is>
           <t>Erkende Natuurreservaten</t>
         </is>
       </c>
-      <c r="FG3" s="61" t="inlineStr">
+      <c r="FG3" s="62" t="inlineStr">
         <is>
           <t>Gebieden duinendecreet</t>
         </is>
       </c>
-      <c r="FH3" s="74" t="inlineStr">
+      <c r="FH3" s="75" t="inlineStr">
         <is>
           <t>Gebieden van het VEN en het IVON
 (VEN en het IVON)</t>
         </is>
       </c>
-      <c r="FI3" s="75" t="inlineStr">
+      <c r="FI3" s="76" t="inlineStr">
         <is>
           <t>Habitatrichtlijngebieden</t>
         </is>
       </c>
-      <c r="FJ3" s="76" t="inlineStr">
+      <c r="FJ3" s="77" t="inlineStr">
         <is>
           <t>Vogelrichtlijngebieden</t>
         </is>
       </c>
-      <c r="FK3" s="20" t="inlineStr">
+      <c r="FK3" s="21" t="inlineStr">
         <is>
           <t>Geluidsbelasting belangrijke wegen Lnight 2021
   (Exposition au bruit- routes)</t>
@@ -2742,7 +2860,7 @@
       <c r="FM3" s="1" t="n"/>
       <c r="FN3" s="1" t="n"/>
       <c r="FO3" s="1" t="n"/>
-      <c r="FP3" s="20" t="inlineStr">
+      <c r="FP3" s="21" t="inlineStr">
         <is>
           <t>Geluidsbelasting belangrijke luchthaven(s) Lnight 2021(Exposition au bruit- voies ferrées)</t>
         </is>
@@ -2751,7 +2869,7 @@
       <c r="FR3" s="1" t="n"/>
       <c r="FS3" s="1" t="n"/>
       <c r="FT3" s="1" t="n"/>
-      <c r="FU3" s="20" t="inlineStr">
+      <c r="FU3" s="21" t="inlineStr">
         <is>
           <t>Geluidsbelasting Geluidsbelasting belangrijke spoorwegen Lden 2021 (Exposition au bruit- aéroport)</t>
         </is>
@@ -2760,32 +2878,32 @@
       <c r="FW3" s="1" t="n"/>
       <c r="FX3" s="1" t="n"/>
       <c r="FY3" s="1" t="n"/>
-      <c r="FZ3" s="82" t="inlineStr">
+      <c r="FZ3" s="83" t="inlineStr">
         <is>
           <t>Bodem is licht verontreinigd</t>
         </is>
       </c>
-      <c r="GA3" s="83" t="inlineStr">
+      <c r="GA3" s="84" t="inlineStr">
         <is>
           <t>Bodem is proper</t>
         </is>
       </c>
-      <c r="GB3" s="84" t="inlineStr">
+      <c r="GB3" s="85" t="inlineStr">
         <is>
           <t>Bodem is verontreinigd</t>
         </is>
       </c>
-      <c r="GC3" s="85" t="inlineStr">
+      <c r="GC3" s="86" t="inlineStr">
         <is>
           <t>Bodeminfo wordt gecheckt</t>
         </is>
       </c>
-      <c r="GD3" s="79" t="inlineStr">
+      <c r="GD3" s="80" t="inlineStr">
         <is>
           <t>Mogelijke risicogrond</t>
         </is>
       </c>
-      <c r="GE3" s="80" t="inlineStr">
+      <c r="GE3" s="81" t="inlineStr">
         <is>
           <t>Geen bodeminfo</t>
         </is>
@@ -2795,956 +2913,941 @@
           <t>Woningbouwgebieden</t>
         </is>
       </c>
-      <c r="GG3" s="77" t="inlineStr">
+      <c r="GG3" s="78" t="inlineStr">
         <is>
           <t>Woonvernieuwingsgebieden</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23.25" customHeight="1">
-      <c r="A4" s="86" t="n"/>
-      <c r="B4" s="86" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C4" s="86" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="D4" s="87" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="E4" s="87" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F4" s="111" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="I4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="J4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="K4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="L4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="M4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="N4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="O4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Q4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="R4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="S4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="T4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="U4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="V4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="W4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="X4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Y4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Z4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AE4" s="88" t="n"/>
-      <c r="AF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AR4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AS4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AT4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BR4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BS4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BT4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CR4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CS4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CT4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DF4" s="104" t="inlineStr">
+      <c r="A4" s="87" t="n"/>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F4" s="112" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="J4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="L4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Q4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="R4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="S4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="T4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="U4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="V4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="W4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="X4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Y4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Z4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AE4" s="89" t="n"/>
+      <c r="AF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DF4" s="105" t="inlineStr">
         <is>
           <t>Geen overstroming gemodelleerd</t>
         </is>
       </c>
-      <c r="DG4" s="105" t="inlineStr">
+      <c r="DG4" s="106" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen onder klimaatverandering</t>
         </is>
       </c>
-      <c r="DH4" s="106" t="inlineStr">
+      <c r="DH4" s="107" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen</t>
         </is>
       </c>
-      <c r="DI4" s="107" t="inlineStr">
+      <c r="DI4" s="108" t="inlineStr">
         <is>
           <t>Middelgrote kans op overstromingen</t>
         </is>
       </c>
-      <c r="DJ4" s="104" t="inlineStr">
+      <c r="DJ4" s="105" t="inlineStr">
         <is>
           <t>Geen overstroming gemodelleerd</t>
         </is>
       </c>
-      <c r="DK4" s="105" t="inlineStr">
+      <c r="DK4" s="106" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen onder klimaatverandering</t>
         </is>
       </c>
-      <c r="DL4" s="106" t="inlineStr">
+      <c r="DL4" s="107" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen</t>
         </is>
       </c>
-      <c r="DM4" s="107" t="inlineStr">
+      <c r="DM4" s="108" t="inlineStr">
         <is>
           <t>Middelgrote kans op overstromingen</t>
         </is>
       </c>
-      <c r="DN4" s="104" t="inlineStr">
+      <c r="DN4" s="105" t="inlineStr">
         <is>
           <t>Geen overstroming gemodelleerd</t>
         </is>
       </c>
-      <c r="DO4" s="105" t="inlineStr">
+      <c r="DO4" s="106" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen onder klimaatverandering</t>
         </is>
       </c>
-      <c r="DP4" s="106" t="inlineStr">
+      <c r="DP4" s="107" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen</t>
         </is>
       </c>
-      <c r="DQ4" s="107" t="inlineStr">
+      <c r="DQ4" s="108" t="inlineStr">
         <is>
           <t>Middelgrote kans op overstromingen</t>
         </is>
       </c>
-      <c r="DR4" s="108" t="inlineStr">
+      <c r="DR4" s="109" t="inlineStr">
         <is>
           <t>IWB OeverzoneI</t>
         </is>
       </c>
-      <c r="DS4" s="108" t="inlineStr">
+      <c r="DS4" s="109" t="inlineStr">
         <is>
           <t>WB Overstromingsgebied</t>
         </is>
       </c>
-      <c r="DT4" s="109" t="inlineStr">
+      <c r="DT4" s="110" t="inlineStr">
         <is>
           <t>Bouwvrije opgave</t>
         </is>
       </c>
-      <c r="DU4" s="110" t="inlineStr">
+      <c r="DU4" s="111" t="inlineStr">
         <is>
           <t>Verscherpte watertoets</t>
         </is>
       </c>
-      <c r="DV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EC4" s="89" t="inlineStr">
+      <c r="DV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EC4" s="90" t="inlineStr">
         <is>
           <t>0,5-5 ha</t>
         </is>
       </c>
-      <c r="ED4" s="90" t="inlineStr">
+      <c r="ED4" s="91" t="inlineStr">
         <is>
           <t>5-10 ha</t>
         </is>
       </c>
-      <c r="EE4" s="91" t="inlineStr">
+      <c r="EE4" s="92" t="inlineStr">
         <is>
           <t>10-20ha</t>
         </is>
       </c>
-      <c r="EF4" s="92" t="inlineStr">
+      <c r="EF4" s="93" t="inlineStr">
         <is>
           <t>20-50 ha</t>
         </is>
       </c>
-      <c r="EG4" s="93" t="inlineStr">
+      <c r="EG4" s="94" t="inlineStr">
         <is>
           <t>50-100 ha</t>
         </is>
       </c>
-      <c r="EH4" s="94" t="inlineStr">
+      <c r="EH4" s="95" t="inlineStr">
         <is>
           <t>&gt;100 ha</t>
         </is>
       </c>
-      <c r="EI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="ER4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="ES4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="ET4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FK4" s="95" t="inlineStr">
+      <c r="EI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="ER4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="ES4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="ET4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FK4" s="96" t="inlineStr">
         <is>
           <t>50-55 dB (décibel)</t>
         </is>
       </c>
-      <c r="FL4" s="96" t="inlineStr">
+      <c r="FL4" s="97" t="inlineStr">
         <is>
           <t>55-60 dB</t>
         </is>
       </c>
-      <c r="FM4" s="97" t="inlineStr">
+      <c r="FM4" s="98" t="inlineStr">
         <is>
           <t>60-65 dB</t>
         </is>
       </c>
-      <c r="FN4" s="98" t="inlineStr">
+      <c r="FN4" s="99" t="inlineStr">
         <is>
           <t>65-70 dB</t>
         </is>
       </c>
-      <c r="FO4" s="99" t="inlineStr">
+      <c r="FO4" s="100" t="inlineStr">
         <is>
           <t>&gt; 70 dB</t>
         </is>
       </c>
-      <c r="FP4" s="95" t="inlineStr">
+      <c r="FP4" s="96" t="inlineStr">
         <is>
           <t>50-55 dB (décibel)</t>
         </is>
       </c>
-      <c r="FQ4" s="96" t="inlineStr">
+      <c r="FQ4" s="97" t="inlineStr">
         <is>
           <t>55-60 dB</t>
         </is>
       </c>
-      <c r="FR4" s="97" t="inlineStr">
+      <c r="FR4" s="98" t="inlineStr">
         <is>
           <t>60-65 dB</t>
         </is>
       </c>
-      <c r="FS4" s="98" t="inlineStr">
+      <c r="FS4" s="99" t="inlineStr">
         <is>
           <t>65-70 dB</t>
         </is>
       </c>
-      <c r="FT4" s="99" t="inlineStr">
+      <c r="FT4" s="100" t="inlineStr">
         <is>
           <t>&gt; 70 dB</t>
         </is>
       </c>
-      <c r="FU4" s="95" t="inlineStr">
+      <c r="FU4" s="96" t="inlineStr">
         <is>
           <t>50-55 dB (décibel)</t>
         </is>
       </c>
-      <c r="FV4" s="96" t="inlineStr">
+      <c r="FV4" s="97" t="inlineStr">
         <is>
           <t>55-60 dB</t>
         </is>
       </c>
-      <c r="FW4" s="97" t="inlineStr">
+      <c r="FW4" s="98" t="inlineStr">
         <is>
           <t>60-65 dB</t>
         </is>
       </c>
-      <c r="FX4" s="98" t="inlineStr">
+      <c r="FX4" s="99" t="inlineStr">
         <is>
           <t>65-70 dB</t>
         </is>
       </c>
-      <c r="FY4" s="99" t="inlineStr">
+      <c r="FY4" s="100" t="inlineStr">
         <is>
           <t>&gt; 70 dB</t>
         </is>
       </c>
-      <c r="FZ4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GA4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GB4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GC4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GF4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GG4" s="100" t="inlineStr">
+      <c r="FZ4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GA4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GB4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GC4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GF4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GG4" s="101" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
     </row>
-    <row r="5" customFormat="1" s="120"/>
-    <row r="6" customFormat="1" s="120"/>
-    <row r="7" customFormat="1" s="120"/>
-    <row r="8" customFormat="1" s="120"/>
-    <row r="9" customFormat="1" s="120"/>
-    <row r="10" customFormat="1" s="120"/>
-    <row r="11" customFormat="1" s="120"/>
-    <row r="12" customFormat="1" s="120"/>
-    <row r="13" customFormat="1" s="120"/>
-    <row r="14" customFormat="1" s="120"/>
-    <row r="15" customFormat="1" s="120"/>
-    <row r="16" customFormat="1" s="120"/>
-    <row r="17" customFormat="1" s="120"/>
-    <row r="18" customFormat="1" s="120"/>
-    <row r="19" customFormat="1" s="125"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="DN3:DQ3"/>
@@ -3756,4 +3859,188 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col width="35.28515625" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="165" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Commune</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Code postal</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Rue</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Numéro</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Numéro cadastral</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Plans d'exécution spatiaux (Région) (Ruimtelijke uitvoeringsplannen RUP- Gewest)</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Chercher commune par commune https://dsi.omgeving.vlaanderen.be/fiche-overzicht?locatie=41002 + indiquer le lien vers le RUP</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Plans d'exécution spatiaux (Province) (Ruimtelijke uitvoeringsplannen RUP- Provincie)</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Chercher commune par commune https://dsi.omgeving.vlaanderen.be/fiche-overzicht?locatie=41002 + indiquer le lien vers le RUP</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Plans d'exécution spatiaux (Commune) (Ruimtelijke uitvoeringsplannen RUP- Gemeente)</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>Chercher commune par commune https://dsi.omgeving.vlaanderen.be/fiche-overzicht?locatie=41002 + indiquer le lien vers le RUP</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="33.75" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="41" t="inlineStr">
+        <is>
+          <t>Lien plan d'execution REGION</t>
+        </is>
+      </c>
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>RUP</t>
+        </is>
+      </c>
+      <c r="H3" s="115" t="n"/>
+      <c r="I3" s="41" t="inlineStr">
+        <is>
+          <t>Lien plman d'execution PROVINCE</t>
+        </is>
+      </c>
+      <c r="J3" s="41" t="inlineStr">
+        <is>
+          <t>RUP</t>
+        </is>
+      </c>
+      <c r="K3" s="115" t="n"/>
+      <c r="L3" s="41" t="inlineStr">
+        <is>
+          <t>Lien  d'execution commune</t>
+        </is>
+      </c>
+      <c r="M3" s="41" t="inlineStr">
+        <is>
+          <t>RUP</t>
+        </is>
+      </c>
+      <c r="N3" s="115" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="87" t="n"/>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H4" s="89" t="n"/>
+      <c r="I4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="J4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K4" s="89" t="n"/>
+      <c r="L4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N4" s="89" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>